--- a/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
+++ b/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
@@ -333,72 +333,76 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -674,130 +678,130 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="2" t="s">
+      <c r="A3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
-      <c r="E3" s="2"/>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-      <c r="H3" s="2"/>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="3"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3"/>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="4"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="4"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="2" t="s">
+      <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
+      <c r="B5" s="3"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="3"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
+      <c r="B6" s="3"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="3"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3"/>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="4"/>
+      <c r="D7" s="4"/>
+      <c r="E7" s="4"/>
+      <c r="F7" s="4"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="2" t="s">
+      <c r="A8" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
+      <c r="B8" s="3"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="2" t="s">
+      <c r="A9" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
+      <c r="B9" s="3"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="3"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="7" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="7" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="7" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="8" t="s">
+      <c r="A16" s="9" t="s">
         <v>15</v>
       </c>
     </row>
@@ -830,439 +834,439 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="1" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="9"/>
-      <c r="C2" s="9"/>
-      <c r="D2" s="9"/>
-      <c r="E2" s="9"/>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9"/>
-      <c r="H2" s="9"/>
-      <c r="I2" s="9"/>
-      <c r="J2" s="9"/>
-      <c r="K2" s="9"/>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+      <c r="F2" s="10"/>
+      <c r="G2" s="10"/>
+      <c r="H2" s="10"/>
+      <c r="I2" s="10"/>
+      <c r="J2" s="10"/>
+      <c r="K2" s="10"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="12" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="11" t="s">
+      <c r="F4" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="11" t="s">
+      <c r="I4" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="11" t="s">
+      <c r="J4" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="12" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="14" t="n">
+      <c r="C5" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="14" t="n">
+      <c r="E5" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="14" t="n">
+      <c r="F5" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="14" t="n">
+      <c r="G5" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="14"/>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="13" t="s">
+      <c r="B6" s="14" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="14" t="n">
+      <c r="C6" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="14" t="n">
+      <c r="E6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="14" t="n">
+      <c r="G6" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="14"/>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
+      <c r="H6" s="15"/>
+      <c r="I6" s="15"/>
+      <c r="J6" s="15"/>
+      <c r="K6" s="15"/>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="13" t="s">
+      <c r="B7" s="14" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="14" t="n">
+      <c r="C7" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="14" t="n">
+      <c r="E7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="14" t="n">
+      <c r="F7" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="14" t="n">
+      <c r="G7" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="14"/>
-      <c r="I7" s="14"/>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
+      <c r="H7" s="15"/>
+      <c r="I7" s="15"/>
+      <c r="J7" s="15"/>
+      <c r="K7" s="15"/>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
+      <c r="A8" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="13" t="s">
+      <c r="B8" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="14" t="n">
+      <c r="C8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="15" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="14"/>
-      <c r="I8" s="14"/>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
+      <c r="H8" s="15"/>
+      <c r="I8" s="15"/>
+      <c r="J8" s="15"/>
+      <c r="K8" s="15"/>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
+      <c r="A9" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="13" t="s">
+      <c r="B9" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="14" t="n">
+      <c r="C9" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="14" t="n">
+      <c r="E9" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="14" t="n">
+      <c r="F9" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="14" t="n">
+      <c r="G9" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="14"/>
-      <c r="I9" s="14"/>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
+      <c r="H9" s="15"/>
+      <c r="I9" s="15"/>
+      <c r="J9" s="15"/>
+      <c r="K9" s="15"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
+      <c r="A10" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="13" t="s">
+      <c r="B10" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="14" t="n">
+      <c r="C10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="14" t="n">
+      <c r="F10" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="15" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="14"/>
-      <c r="I10" s="14"/>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
+      <c r="H10" s="15"/>
+      <c r="I10" s="15"/>
+      <c r="J10" s="15"/>
+      <c r="K10" s="15"/>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="13" t="s">
+      <c r="B11" s="14" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="14" t="n">
+      <c r="C11" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="15" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="14" t="n">
+      <c r="G11" s="15" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
+      <c r="H11" s="15"/>
+      <c r="I11" s="15"/>
+      <c r="J11" s="15"/>
+      <c r="K11" s="15"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="15" t="s">
+      <c r="A12" s="16" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="16" t="n">
+      <c r="D12" s="17" t="n">
         <f aca="false">IF(COUNT(D5:D11)=0,"",SUMPRODUCT($C$5:$C$11,D5:D11))</f>
         <v>28</v>
       </c>
-      <c r="E12" s="16" t="n">
+      <c r="E12" s="17" t="n">
         <f aca="false">IF(COUNT(E5:E11)=0,"",SUMPRODUCT($C$5:$C$11,E5:E11))</f>
         <v>23</v>
       </c>
-      <c r="F12" s="16" t="n">
+      <c r="F12" s="17" t="n">
         <f aca="false">IF(COUNT(F5:F11)=0,"",SUMPRODUCT($C$5:$C$11,F5:F11))</f>
         <v>18</v>
       </c>
-      <c r="G12" s="16" t="n">
+      <c r="G12" s="17" t="n">
         <f aca="false">IF(COUNT(G5:G11)=0,"",SUMPRODUCT($C$5:$C$11,G5:G11))</f>
         <v>21</v>
       </c>
-      <c r="H12" s="16" t="str">
+      <c r="H12" s="17" t="str">
         <f aca="false">IF(COUNT(H5:H11)=0,"",SUMPRODUCT($C$5:$C$11,H5:H11))</f>
         <v/>
       </c>
-      <c r="I12" s="16" t="str">
+      <c r="I12" s="17" t="str">
         <f aca="false">IF(COUNT(I5:I11)=0,"",SUMPRODUCT($C$5:$C$11,I5:I11))</f>
         <v/>
       </c>
-      <c r="J12" s="16" t="str">
+      <c r="J12" s="17" t="str">
         <f aca="false">IF(COUNT(J5:J11)=0,"",SUMPRODUCT($C$5:$C$11,J5:J11))</f>
         <v/>
       </c>
-      <c r="K12" s="16" t="str">
+      <c r="K12" s="17" t="str">
         <f aca="false">IF(COUNT(K5:K11)=0,"",SUMPRODUCT($C$5:$C$11,K5:K11))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="15" t="s">
+      <c r="A13" s="16" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="16" t="n">
+      <c r="D13" s="17" t="n">
         <f aca="false">IF(D12="","",ROUND(D12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>80</v>
       </c>
-      <c r="E13" s="16" t="n">
+      <c r="E13" s="17" t="n">
         <f aca="false">IF(E12="","",ROUND(E12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>66</v>
       </c>
-      <c r="F13" s="16" t="n">
+      <c r="F13" s="17" t="n">
         <f aca="false">IF(F12="","",ROUND(F12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>51</v>
       </c>
-      <c r="G13" s="16" t="n">
+      <c r="G13" s="17" t="n">
         <f aca="false">IF(G12="","",ROUND(G12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>60</v>
       </c>
-      <c r="H13" s="16" t="str">
+      <c r="H13" s="17" t="str">
         <f aca="false">IF(H12="","",ROUND(H12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="I13" s="16" t="str">
+      <c r="I13" s="17" t="str">
         <f aca="false">IF(I12="","",ROUND(I12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="J13" s="16" t="str">
+      <c r="J13" s="17" t="str">
         <f aca="false">IF(J12="","",ROUND(J12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="K13" s="16" t="str">
+      <c r="K13" s="17" t="str">
         <f aca="false">IF(K12="","",ROUND(K12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="15" t="s">
+      <c r="A14" s="16" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="16" t="n">
+      <c r="D14" s="17" t="n">
         <f aca="false">IF(D12="","",RANK(D12,$D$12:$K$12))</f>
         <v>1</v>
       </c>
-      <c r="E14" s="16" t="n">
+      <c r="E14" s="17" t="n">
         <f aca="false">IF(E12="","",RANK(E12,$D$12:$K$12))</f>
         <v>2</v>
       </c>
-      <c r="F14" s="16" t="n">
+      <c r="F14" s="17" t="n">
         <f aca="false">IF(F12="","",RANK(F12,$D$12:$K$12))</f>
         <v>4</v>
       </c>
-      <c r="G14" s="16" t="n">
+      <c r="G14" s="17" t="n">
         <f aca="false">IF(G12="","",RANK(G12,$D$12:$K$12))</f>
         <v>3</v>
       </c>
-      <c r="H14" s="16" t="str">
+      <c r="H14" s="17" t="str">
         <f aca="false">IF(H12="","",RANK(H12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="I14" s="16" t="str">
+      <c r="I14" s="17" t="str">
         <f aca="false">IF(I12="","",RANK(I12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="J14" s="16" t="str">
+      <c r="J14" s="17" t="str">
         <f aca="false">IF(J12="","",RANK(J12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="K14" s="16" t="str">
+      <c r="K14" s="17" t="str">
         <f aca="false">IF(K12="","",RANK(K12,$D$12:$K$12))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="16" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="14"/>
-      <c r="B17" s="14"/>
-      <c r="C17" s="14"/>
-      <c r="D17" s="14"/>
-      <c r="E17" s="14"/>
-      <c r="F17" s="14"/>
-      <c r="G17" s="14"/>
-      <c r="H17" s="14"/>
-      <c r="I17" s="14"/>
-      <c r="J17" s="14"/>
-      <c r="K17" s="14"/>
+      <c r="A17" s="15"/>
+      <c r="B17" s="15"/>
+      <c r="C17" s="15"/>
+      <c r="D17" s="15"/>
+      <c r="E17" s="15"/>
+      <c r="F17" s="15"/>
+      <c r="G17" s="15"/>
+      <c r="H17" s="15"/>
+      <c r="I17" s="15"/>
+      <c r="J17" s="15"/>
+      <c r="K17" s="15"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="14"/>
-      <c r="B18" s="14"/>
-      <c r="C18" s="14"/>
-      <c r="D18" s="14"/>
-      <c r="E18" s="14"/>
-      <c r="F18" s="14"/>
-      <c r="G18" s="14"/>
-      <c r="H18" s="14"/>
-      <c r="I18" s="14"/>
-      <c r="J18" s="14"/>
-      <c r="K18" s="14"/>
+      <c r="A18" s="15"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+      <c r="F18" s="15"/>
+      <c r="G18" s="15"/>
+      <c r="H18" s="15"/>
+      <c r="I18" s="15"/>
+      <c r="J18" s="15"/>
+      <c r="K18" s="15"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
-      <c r="E19" s="14"/>
-      <c r="F19" s="14"/>
-      <c r="G19" s="14"/>
-      <c r="H19" s="14"/>
-      <c r="I19" s="14"/>
-      <c r="J19" s="14"/>
-      <c r="K19" s="14"/>
+      <c r="A19" s="15"/>
+      <c r="B19" s="15"/>
+      <c r="C19" s="15"/>
+      <c r="D19" s="15"/>
+      <c r="E19" s="15"/>
+      <c r="F19" s="15"/>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15"/>
+      <c r="I19" s="15"/>
+      <c r="J19" s="15"/>
+      <c r="K19" s="15"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
-      <c r="G20" s="14"/>
-      <c r="H20" s="14"/>
-      <c r="I20" s="14"/>
-      <c r="J20" s="14"/>
-      <c r="K20" s="14"/>
+      <c r="A20" s="15"/>
+      <c r="B20" s="15"/>
+      <c r="C20" s="15"/>
+      <c r="D20" s="15"/>
+      <c r="E20" s="15"/>
+      <c r="F20" s="15"/>
+      <c r="G20" s="15"/>
+      <c r="H20" s="15"/>
+      <c r="I20" s="15"/>
+      <c r="J20" s="15"/>
+      <c r="K20" s="15"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
-      <c r="G21" s="14"/>
-      <c r="H21" s="14"/>
-      <c r="I21" s="14"/>
-      <c r="J21" s="14"/>
-      <c r="K21" s="14"/>
+      <c r="A21" s="15"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="15"/>
+      <c r="D21" s="15"/>
+      <c r="E21" s="15"/>
+      <c r="F21" s="15"/>
+      <c r="G21" s="15"/>
+      <c r="H21" s="15"/>
+      <c r="I21" s="15"/>
+      <c r="J21" s="15"/>
+      <c r="K21" s="15"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="8" t="s">
+      <c r="A23" s="9" t="s">
         <v>47</v>
       </c>
     </row>

--- a/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
+++ b/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
@@ -333,76 +333,72 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="11" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="165" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -678,130 +674,130 @@
   <dimension ref="A1:H16"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="2" style="0" width="14"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="3"/>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="2"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="2"/>
+      <c r="H3" s="2"/>
     </row>
     <row r="4" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4"/>
+      <c r="B4" s="3"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="3"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="3"/>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3"/>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="2"/>
+      <c r="H5" s="2"/>
     </row>
     <row r="6" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="3"/>
-      <c r="C6" s="3"/>
-      <c r="D6" s="3"/>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2"/>
+      <c r="H6" s="2"/>
     </row>
     <row r="7" customFormat="false" ht="15.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4"/>
+      <c r="B7" s="3"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3"/>
+      <c r="G7" s="3"/>
+      <c r="H7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="3"/>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="2"/>
+      <c r="H8" s="2"/>
     </row>
     <row r="9" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3"/>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="2"/>
+      <c r="H9" s="2"/>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="B12" s="6" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B13" s="7" t="s">
+      <c r="B13" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="8" t="s">
+      <c r="A14" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="7" t="s">
+      <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="9" t="s">
+      <c r="A16" s="8" t="s">
         <v>15</v>
       </c>
     </row>
@@ -834,439 +830,439 @@
   <dimension ref="A1:K23"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="8"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="1" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="4" style="0" width="10"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="19.7" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="10"/>
-      <c r="E2" s="10"/>
-      <c r="F2" s="10"/>
-      <c r="G2" s="10"/>
-      <c r="H2" s="10"/>
-      <c r="I2" s="10"/>
-      <c r="J2" s="10"/>
-      <c r="K2" s="10"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
+      <c r="K2" s="9"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B4" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C4" s="11" t="s">
+      <c r="C4" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="H4" s="12" t="s">
+      <c r="H4" s="11" t="s">
         <v>25</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="J4" s="12" t="s">
+      <c r="J4" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="K4" s="12" t="s">
+      <c r="K4" s="11" t="s">
         <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="13" t="s">
+      <c r="A5" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="B5" s="14" t="s">
+      <c r="B5" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C5" s="15" t="n">
+      <c r="C5" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D5" s="15" t="n">
+      <c r="D5" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E5" s="15" t="n">
+      <c r="E5" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G5" s="15" t="n">
+      <c r="G5" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H5" s="15"/>
-      <c r="I5" s="15"/>
-      <c r="J5" s="15"/>
-      <c r="K5" s="15"/>
+      <c r="H5" s="14"/>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
     </row>
     <row r="6" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="B6" s="14" t="s">
+      <c r="B6" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="15" t="n">
+      <c r="C6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D6" s="15" t="n">
+      <c r="D6" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E6" s="15" t="n">
+      <c r="E6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="F6" s="15" t="n">
+      <c r="F6" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G6" s="15" t="n">
+      <c r="G6" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H6" s="15"/>
-      <c r="I6" s="15"/>
-      <c r="J6" s="15"/>
-      <c r="K6" s="15"/>
+      <c r="H6" s="14"/>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
     </row>
     <row r="7" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="13" t="s">
+      <c r="A7" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="B7" s="14" t="s">
+      <c r="B7" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C7" s="15" t="n">
+      <c r="C7" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D7" s="15" t="n">
+      <c r="D7" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G7" s="15" t="n">
+      <c r="G7" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H7" s="15"/>
-      <c r="I7" s="15"/>
-      <c r="J7" s="15"/>
-      <c r="K7" s="15"/>
+      <c r="H7" s="14"/>
+      <c r="I7" s="14"/>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
     </row>
     <row r="8" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="13" t="s">
+      <c r="A8" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="14" t="s">
+      <c r="B8" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C8" s="15" t="n">
+      <c r="C8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D8" s="15" t="n">
+      <c r="D8" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="E8" s="15" t="n">
+      <c r="E8" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F8" s="15" t="n">
+      <c r="F8" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G8" s="15" t="n">
+      <c r="G8" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="H8" s="15"/>
-      <c r="I8" s="15"/>
-      <c r="J8" s="15"/>
-      <c r="K8" s="15"/>
+      <c r="H8" s="14"/>
+      <c r="I8" s="14"/>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
     </row>
     <row r="9" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="13" t="s">
+      <c r="A9" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="14" t="s">
+      <c r="B9" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C9" s="15" t="n">
+      <c r="C9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E9" s="15" t="n">
+      <c r="E9" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="G9" s="15" t="n">
+      <c r="G9" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H9" s="15"/>
-      <c r="I9" s="15"/>
-      <c r="J9" s="15"/>
-      <c r="K9" s="15"/>
+      <c r="H9" s="14"/>
+      <c r="I9" s="14"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="13" t="s">
+      <c r="A10" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="14" t="s">
+      <c r="B10" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="C10" s="15" t="n">
+      <c r="C10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="E10" s="15" t="n">
+      <c r="E10" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="F10" s="15" t="n">
+      <c r="F10" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="15" t="n">
+      <c r="G10" s="14" t="n">
         <v>2</v>
       </c>
-      <c r="H10" s="15"/>
-      <c r="I10" s="15"/>
-      <c r="J10" s="15"/>
-      <c r="K10" s="15"/>
+      <c r="H10" s="14"/>
+      <c r="I10" s="14"/>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
     </row>
     <row r="11" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="14" t="s">
+      <c r="B11" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="C11" s="15" t="n">
+      <c r="C11" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="15" t="n">
+      <c r="D11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="E11" s="15" t="n">
+      <c r="E11" s="14" t="n">
         <v>4</v>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="G11" s="15" t="n">
+      <c r="G11" s="14" t="n">
         <v>3</v>
       </c>
-      <c r="H11" s="15"/>
-      <c r="I11" s="15"/>
-      <c r="J11" s="15"/>
-      <c r="K11" s="15"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="16" t="s">
+      <c r="A12" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="D12" s="17" t="n">
+      <c r="D12" s="16" t="n">
         <f aca="false">IF(COUNT(D5:D11)=0,"",SUMPRODUCT($C$5:$C$11,D5:D11))</f>
         <v>28</v>
       </c>
-      <c r="E12" s="17" t="n">
+      <c r="E12" s="16" t="n">
         <f aca="false">IF(COUNT(E5:E11)=0,"",SUMPRODUCT($C$5:$C$11,E5:E11))</f>
         <v>23</v>
       </c>
-      <c r="F12" s="17" t="n">
+      <c r="F12" s="16" t="n">
         <f aca="false">IF(COUNT(F5:F11)=0,"",SUMPRODUCT($C$5:$C$11,F5:F11))</f>
         <v>18</v>
       </c>
-      <c r="G12" s="17" t="n">
+      <c r="G12" s="16" t="n">
         <f aca="false">IF(COUNT(G5:G11)=0,"",SUMPRODUCT($C$5:$C$11,G5:G11))</f>
         <v>21</v>
       </c>
-      <c r="H12" s="17" t="str">
+      <c r="H12" s="16" t="str">
         <f aca="false">IF(COUNT(H5:H11)=0,"",SUMPRODUCT($C$5:$C$11,H5:H11))</f>
         <v/>
       </c>
-      <c r="I12" s="17" t="str">
+      <c r="I12" s="16" t="str">
         <f aca="false">IF(COUNT(I5:I11)=0,"",SUMPRODUCT($C$5:$C$11,I5:I11))</f>
         <v/>
       </c>
-      <c r="J12" s="17" t="str">
+      <c r="J12" s="16" t="str">
         <f aca="false">IF(COUNT(J5:J11)=0,"",SUMPRODUCT($C$5:$C$11,J5:J11))</f>
         <v/>
       </c>
-      <c r="K12" s="17" t="str">
+      <c r="K12" s="16" t="str">
         <f aca="false">IF(COUNT(K5:K11)=0,"",SUMPRODUCT($C$5:$C$11,K5:K11))</f>
         <v/>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="D13" s="17" t="n">
+      <c r="D13" s="16" t="n">
         <f aca="false">IF(D12="","",ROUND(D12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>80</v>
       </c>
-      <c r="E13" s="17" t="n">
+      <c r="E13" s="16" t="n">
         <f aca="false">IF(E12="","",ROUND(E12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>66</v>
       </c>
-      <c r="F13" s="17" t="n">
+      <c r="F13" s="16" t="n">
         <f aca="false">IF(F12="","",ROUND(F12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>51</v>
       </c>
-      <c r="G13" s="17" t="n">
+      <c r="G13" s="16" t="n">
         <f aca="false">IF(G12="","",ROUND(G12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v>60</v>
       </c>
-      <c r="H13" s="17" t="str">
+      <c r="H13" s="16" t="str">
         <f aca="false">IF(H12="","",ROUND(H12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="I13" s="17" t="str">
+      <c r="I13" s="16" t="str">
         <f aca="false">IF(I12="","",ROUND(I12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="J13" s="17" t="str">
+      <c r="J13" s="16" t="str">
         <f aca="false">IF(J12="","",ROUND(J12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
-      <c r="K13" s="17" t="str">
+      <c r="K13" s="16" t="str">
         <f aca="false">IF(K12="","",ROUND(K12/(5*SUM($C$5:$C$11))*100,0))</f>
         <v/>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>45</v>
       </c>
-      <c r="D14" s="17" t="n">
+      <c r="D14" s="16" t="n">
         <f aca="false">IF(D12="","",RANK(D12,$D$12:$K$12))</f>
         <v>1</v>
       </c>
-      <c r="E14" s="17" t="n">
+      <c r="E14" s="16" t="n">
         <f aca="false">IF(E12="","",RANK(E12,$D$12:$K$12))</f>
         <v>2</v>
       </c>
-      <c r="F14" s="17" t="n">
+      <c r="F14" s="16" t="n">
         <f aca="false">IF(F12="","",RANK(F12,$D$12:$K$12))</f>
         <v>4</v>
       </c>
-      <c r="G14" s="17" t="n">
+      <c r="G14" s="16" t="n">
         <f aca="false">IF(G12="","",RANK(G12,$D$12:$K$12))</f>
         <v>3</v>
       </c>
-      <c r="H14" s="17" t="str">
+      <c r="H14" s="16" t="str">
         <f aca="false">IF(H12="","",RANK(H12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="I14" s="17" t="str">
+      <c r="I14" s="16" t="str">
         <f aca="false">IF(I12="","",RANK(I12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="J14" s="17" t="str">
+      <c r="J14" s="16" t="str">
         <f aca="false">IF(J12="","",RANK(J12,$D$12:$K$12))</f>
         <v/>
       </c>
-      <c r="K14" s="17" t="str">
+      <c r="K14" s="16" t="str">
         <f aca="false">IF(K12="","",RANK(K12,$D$12:$K$12))</f>
         <v/>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="16" t="s">
+      <c r="A16" s="15" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="15"/>
-      <c r="B17" s="15"/>
-      <c r="C17" s="15"/>
-      <c r="D17" s="15"/>
-      <c r="E17" s="15"/>
-      <c r="F17" s="15"/>
-      <c r="G17" s="15"/>
-      <c r="H17" s="15"/>
-      <c r="I17" s="15"/>
-      <c r="J17" s="15"/>
-      <c r="K17" s="15"/>
+      <c r="A17" s="14"/>
+      <c r="B17" s="14"/>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="15"/>
-      <c r="B18" s="15"/>
-      <c r="C18" s="15"/>
-      <c r="D18" s="15"/>
-      <c r="E18" s="15"/>
-      <c r="F18" s="15"/>
-      <c r="G18" s="15"/>
-      <c r="H18" s="15"/>
-      <c r="I18" s="15"/>
-      <c r="J18" s="15"/>
-      <c r="K18" s="15"/>
+      <c r="A18" s="14"/>
+      <c r="B18" s="14"/>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="15"/>
-      <c r="B19" s="15"/>
-      <c r="C19" s="15"/>
-      <c r="D19" s="15"/>
-      <c r="E19" s="15"/>
-      <c r="F19" s="15"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="15"/>
-      <c r="I19" s="15"/>
-      <c r="J19" s="15"/>
-      <c r="K19" s="15"/>
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="15"/>
-      <c r="B20" s="15"/>
-      <c r="C20" s="15"/>
-      <c r="D20" s="15"/>
-      <c r="E20" s="15"/>
-      <c r="F20" s="15"/>
-      <c r="G20" s="15"/>
-      <c r="H20" s="15"/>
-      <c r="I20" s="15"/>
-      <c r="J20" s="15"/>
-      <c r="K20" s="15"/>
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="15"/>
-      <c r="B21" s="15"/>
-      <c r="C21" s="15"/>
-      <c r="D21" s="15"/>
-      <c r="E21" s="15"/>
-      <c r="F21" s="15"/>
-      <c r="G21" s="15"/>
-      <c r="H21" s="15"/>
-      <c r="I21" s="15"/>
-      <c r="J21" s="15"/>
-      <c r="K21" s="15"/>
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="9" t="s">
+      <c r="A23" s="8" t="s">
         <v>47</v>
       </c>
     </row>

--- a/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
+++ b/public/downloads/shopfloor-matters-first-line-scorecard.xlsx
@@ -113,7 +113,7 @@
     <t xml:space="preserve">How much does its downtime or scrap cost?</t>
   </si>
   <si>
-    <t xml:space="preserve">Value you can measure is what funds the next phase.</t>
+    <t xml:space="preserve">Value you can measure is what builds momentum for the programme.</t>
   </si>
   <si>
     <t xml:space="preserve">Is it the bottleneck, or close to it?</t>
